--- a/src/views/game/zlzq/cardList/yiersansiwuCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/yiersansiwuCard/z_level.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="8340" windowHeight="9735" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="11190" windowHeight="9990" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="冬神" sheetId="10" r:id="rId1"/>
     <sheet name="港口" sheetId="8" r:id="rId2"/>
     <sheet name="禅意" sheetId="6" r:id="rId3"/>
+    <sheet name="12345" sheetId="11" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
   <si>
     <t>名称</t>
   </si>
@@ -43,18 +44,12 @@
     <t>骨爆</t>
   </si>
   <si>
-    <t>噬魂骨妖</t>
-  </si>
-  <si>
     <t>寒风草人</t>
   </si>
   <si>
     <t>极地狂信者</t>
   </si>
   <si>
-    <t>骸骨前线</t>
-  </si>
-  <si>
     <t>小计：</t>
   </si>
   <si>
@@ -64,12 +59,12 @@
     <t>冬夜使者</t>
   </si>
   <si>
-    <t>寒彻骨</t>
-  </si>
-  <si>
     <t>传记·荒芜之地</t>
   </si>
   <si>
+    <t>符文·天寒地冻</t>
+  </si>
+  <si>
     <t>寒盲刀客</t>
   </si>
   <si>
@@ -88,6 +83,9 @@
     <t>寒风血刃</t>
   </si>
   <si>
+    <t>不息之灵</t>
+  </si>
+  <si>
     <t>永夜女王</t>
   </si>
   <si>
@@ -112,6 +110,9 @@
     <t>黑夜突袭</t>
   </si>
   <si>
+    <t>无声攫取</t>
+  </si>
+  <si>
     <t>酗酒醉汉</t>
   </si>
   <si>
@@ -127,9 +128,6 @@
     <t>黑金诈术师</t>
   </si>
   <si>
-    <t>寻宝队长</t>
-  </si>
-  <si>
     <t>花剑绅士·翔</t>
   </si>
   <si>
@@ -142,12 +140,12 @@
     <t>魔卡幻术师·梅基</t>
   </si>
   <si>
+    <t>符文·海皇之怒</t>
+  </si>
+  <si>
     <t>钢之咆哮·布瑞恩</t>
   </si>
   <si>
-    <t>黑金三代目·梅森</t>
-  </si>
-  <si>
     <t>港口卡等：</t>
   </si>
   <si>
@@ -163,37 +161,34 @@
     <t>黑松林货郎</t>
   </si>
   <si>
+    <t>寒窗才子</t>
+  </si>
+  <si>
+    <t>符文·疾风图腾</t>
+  </si>
+  <si>
     <t>植甲师</t>
   </si>
   <si>
+    <t>宫廷乐师</t>
+  </si>
+  <si>
     <t>扫叶僧</t>
   </si>
   <si>
-    <t>雪山飞狐</t>
-  </si>
-  <si>
-    <t>萌化术</t>
-  </si>
-  <si>
-    <t>渡船隐士</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>寒霜寺护院僧</t>
+    <t>当铺掌柜</t>
   </si>
   <si>
     <t>流岚刃·琳</t>
   </si>
   <si>
+    <t>雪域春光·凛</t>
+  </si>
+  <si>
+    <t>三熊阵</t>
+  </si>
+  <si>
     <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>雪域春光·凛</t>
-  </si>
-  <si>
-    <t>三熊阵</t>
   </si>
   <si>
     <t>禅意卡等：</t>
@@ -1160,7 +1155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1168,7 +1163,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1179,7 +1174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1187,10 +1182,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1198,66 +1193,66 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>21</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="C10" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>19.8</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1265,43 +1260,43 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1309,51 +1304,51 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="C19" s="2">
+        <f>AVERAGE(C10:C16)</f>
+        <v>20.4285714285714</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4</v>
-      </c>
-      <c r="C18" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C23" s="3">
         <v>17</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C12:C18)</f>
-        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1361,10 +1356,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1383,22 +1378,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="3">
-        <v>6</v>
-      </c>
-      <c r="C27" s="3">
-        <v>17</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1406,32 +1395,27 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C22:C26)</f>
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C6,C12:C18,C24:C27)</f>
-        <v>19.5</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1451,7 +1435,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1462,129 +1446,129 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>17.6</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>18</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C12" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="C13" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B14" s="2">
         <v>3</v>
       </c>
-      <c r="C13" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>4</v>
-      </c>
-      <c r="C14" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="B15" s="2">
         <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1596,80 +1580,80 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2">
-        <f>AVERAGE(C12:C15)</f>
-        <v>15.25</v>
+        <f>AVERAGE(C13:C15)</f>
+        <v>17.6666666666667</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
       </c>
       <c r="C21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3">
         <v>3</v>
       </c>
       <c r="C22" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3">
         <v>4</v>
       </c>
       <c r="C23" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1684,26 +1668,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C21:C26)</f>
-        <v>14.8333333333333</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C6,C12:C15,C21:C26)</f>
-        <v>15.8666666666667</v>
+        <f>AVERAGE(C2:C7,C13:C15,C21:C26)</f>
+        <v>16.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1715,7 +1699,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1723,7 +1707,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1734,9 +1718,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1745,149 +1729,143 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>16.6</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>16.1428571428571</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2">
         <v>2</v>
       </c>
-      <c r="C12" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2">
-        <v>16</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1895,47 +1873,53 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C12:C18)</f>
-        <v>15.1428571428571</v>
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C14:C17)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -1945,15 +1929,9 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>13</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1961,36 +1939,42 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C6,C12:C18,C24:C27)</f>
-        <v>15.375</v>
+      <c r="B32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>